--- a/data/project-board.xlsx
+++ b/data/project-board.xlsx
@@ -11138,12 +11138,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Release Generic Edition</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Release Anaplan Edition (v2)</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -13408,13 +13408,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" customWidth="1" min="1" max="1"/>
     <col width="24.83203125" customWidth="1" min="2" max="2"/>
     <col width="12.83203125" customWidth="1" min="3" max="3"/>
-    <col width="14.83203125" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13435,7 +13436,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Release Date</t>
+          <t>Dev Done Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rollout Date</t>
         </is>
       </c>
     </row>
@@ -13460,6 +13466,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13482,6 +13493,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13504,6 +13520,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13543,6 +13564,11 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13565,6 +13591,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13587,6 +13618,11 @@
           <t>2026-11-23</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13609,6 +13645,11 @@
           <t>2026-05-11</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13631,6 +13672,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13653,6 +13699,11 @@
           <t>2026-12-14</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13675,6 +13726,11 @@
           <t>2026-03-09</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13697,6 +13753,11 @@
           <t>2026-07-27</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13719,6 +13780,11 @@
           <t>2026-11-09</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13733,12 +13799,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Generic Edition</t>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -13755,12 +13826,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Anaplan Edition (v2)</t>
+          <t>v2.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -13785,6 +13861,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13805,6 +13886,11 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/data/project-board.xlsx
+++ b/data/project-board.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1982,7 +1982,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2014,10 +2014,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Group Description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Feature Description</t>
         </is>
@@ -2045,6 +2050,9 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2068,6 +2076,9 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2091,6 +2102,9 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2114,6 +2128,9 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2137,6 +2154,9 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2160,6 +2180,9 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2183,6 +2206,9 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2206,6 +2232,9 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2229,6 +2258,9 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2252,6 +2284,9 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2275,6 +2310,9 @@
       <c r="E12" t="n">
         <v>1</v>
       </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2298,27 +2336,33 @@
       <c r="E13" t="n">
         <v>1</v>
       </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAFETY, GUARDRAILS &amp; QA</t>
+          <t>AGENT CORE &amp; ORCHESTRATION</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOQL safety pipeline (guardrails)</t>
+          <t>Core Engine improvements</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Single-statement check</t>
+          <t>Plan revision when a tool call fails mid-run</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2335,13 +2379,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SOQL-injection guardrail</t>
+          <t>Single-statement check</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2353,18 +2400,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Write actions (staging / HITL)</t>
+          <t>SOQL safety pipeline (guardrails)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emit-only: backend never performs the write</t>
+          <t>SOQL-injection guardrail</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2381,13 +2431,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Record-context disambiguation rules</t>
+          <t>Emit-only: backend never performs the write</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2399,18 +2452,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nemo Guardrails</t>
+          <t>Write actions (staging / HITL)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rule-based guardrails for preventing prompt injections</t>
+          <t>Record-context disambiguation rules</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2422,64 +2478,73 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Automated QA for SOQL</t>
+          <t>Write actions (staging / HITL)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Automated tests on generated SOQL</t>
+          <t>Bulk approval queue for staged write actions</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DATA, CACHING &amp; RETRIEVAL</t>
+          <t>SAFETY, GUARDRAILS &amp; QA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Postgres (persistence layer)</t>
+          <t>Nemo Guardrails</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Conversation turn history</t>
+          <t>Rule-based guardrails for preventing prompt injections</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DATA, CACHING &amp; RETRIEVAL</t>
+          <t>SAFETY, GUARDRAILS &amp; QA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Postgres (persistence layer)</t>
+          <t>Automated QA for SOQL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Usage/activity logging: tokens, cost, latency, generated SOQL, row counts, tools used</t>
+          <t>Automated tests on generated SOQL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2496,13 +2561,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Source of truth so any pod can serve any conversation</t>
+          <t>Conversation turn history</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2514,18 +2582,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data Layer (Resource Group)</t>
+          <t>Postgres (persistence layer)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Include current SF schema with Postgres</t>
+          <t>Usage/activity logging: tokens, cost, latency, generated SOQL, row counts, tools used</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2537,18 +2608,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Data Layer (Resource Group)</t>
+          <t>Postgres (persistence layer)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Support Snowflake natively</t>
+          <t>Source of truth so any pod can serve any conversation</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2560,18 +2634,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caching (AWS Valkeys) + in-memory SOQL updates</t>
+          <t>Data Layer (Resource Group)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Updated logic</t>
+          <t>Include current SF schema with Postgres</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2583,18 +2660,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caching (AWS Valkeys) + in-memory SOQL updates</t>
+          <t>Data Layer (Resource Group)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Better semantics</t>
+          <t>Support Snowflake natively</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2606,18 +2686,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RAG Engine (Postgres + OpenSearch + Slack native)</t>
+          <t>Caching (AWS Valkeys) + in-memory SOQL updates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>Updated logic</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2629,156 +2712,177 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RAG Engine (Postgres + OpenSearch + Slack native)</t>
+          <t>Caching (AWS Valkeys) + in-memory SOQL updates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slack integration</t>
+          <t>Better semantics</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SALESFORCE INTEGRATION</t>
+          <t>DATA, CACHING &amp; RETRIEVAL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce auth (OAuth 2.0 JWT Bearer, RS256)</t>
+          <t>RAG Engine (Postgres + OpenSearch + Slack native)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Outbound-only: backend to Salesforce</t>
+          <t>Data layer</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SALESFORCE INTEGRATION</t>
+          <t>DATA, CACHING &amp; RETRIEVAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salesforce auth (OAuth 2.0 JWT Bearer, RS256)</t>
+          <t>RAG Engine (Postgres + OpenSearch + Slack native)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Per-request JWT built and RS256-signed</t>
+          <t>Slack integration</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLATFORM &amp; PROVISIONING</t>
+          <t>DATA, CACHING &amp; RETRIEVAL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>API for creating new VM environments</t>
+          <t>RAG Engine (Postgres + OpenSearch + Slack native)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>API for creating new VM environments</t>
+          <t>Per-object relevance tuning for retrieval</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLATFORM &amp; PROVISIONING</t>
+          <t>SALESFORCE INTEGRATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>API for creating new VM environments</t>
+          <t>Salesforce auth (OAuth 2.0 JWT Bearer, RS256)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Automates Terraform execution (init, fmt, validate, apply)</t>
+          <t>Outbound-only: backend to Salesforce</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLATFORM &amp; PROVISIONING</t>
+          <t>SALESFORCE INTEGRATION</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>API for creating new VM environments</t>
+          <t>Salesforce auth (OAuth 2.0 JWT Bearer, RS256)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Generates client-specific API keys</t>
+          <t>Per-request JWT built and RS256-signed</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLATFORM &amp; PROVISIONING</t>
+          <t>SALESFORCE INTEGRATION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>API for creating new VM environments</t>
+          <t>Salesforce auth (OAuth 2.0 JWT Bearer, RS256)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Generates Salesforce certificate and private key</t>
+          <t>Multi-org connections with per-org scoping</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2795,13 +2899,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dynamically injects API key into .env</t>
+          <t>API for creating new VM environments</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2818,13 +2925,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dynamically injects Salesforce configuration into .env</t>
+          <t>Automates Terraform execution (init, fmt, validate, apply)</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2841,13 +2951,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Injects Salesforce certificate/private key into the deployment</t>
+          <t>Generates client-specific API keys</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2864,13 +2977,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mounts certificate files into the ActioX backend container</t>
+          <t>Generates Salesforce certificate and private key</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2887,13 +3003,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Builds client-specific Salesforce token/query endpoints</t>
+          <t>Dynamically injects API key into .env</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2910,13 +3029,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Validates customer provisioning payloads</t>
+          <t>Dynamically injects Salesforce configuration into .env</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2933,13 +3055,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tracks provisioning jobs and status</t>
+          <t>Injects Salesforce certificate/private key into the deployment</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2956,13 +3081,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Provides provisioning, plan, status, log and destroy APIs</t>
+          <t>Mounts certificate files into the ActioX backend container</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2979,13 +3107,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redacts API keys, Salesforce keys and private keys from logs</t>
+          <t>Builds client-specific Salesforce token/query endpoints</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3002,13 +3133,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Supports API-key rotation</t>
+          <t>Validates customer provisioning payloads</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3025,13 +3159,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Supports Salesforce certificate/key rotation</t>
+          <t>Tracks provisioning jobs and status</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3048,13 +3185,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Maintains backups of previous .env and certificate/key files</t>
+          <t>Provides provisioning, plan, status, log and destroy APIs</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3071,13 +3211,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prevents concurrent Terraform provisioning operations</t>
+          <t>Redacts API keys, Salesforce keys and private keys from logs</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3094,13 +3237,120 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Supports API-key rotation</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PLATFORM &amp; PROVISIONING</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>API for creating new VM environments</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Supports Salesforce certificate/key rotation</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PLATFORM &amp; PROVISIONING</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>API for creating new VM environments</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Maintains backups of previous .env and certificate/key files</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PLATFORM &amp; PROVISIONING</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>API for creating new VM environments</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Prevents concurrent Terraform provisioning operations</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PLATFORM &amp; PROVISIONING</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>API for creating new VM environments</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Provides post-provisioning deployment status and logs</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13408,7 +13658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" customWidth="1" min="1" max="1"/>
@@ -13490,12 +13740,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13767,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-11-25</t>
         </is>
       </c>
     </row>
@@ -13804,12 +14054,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
@@ -13831,12 +14081,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -13858,12 +14108,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -13885,12 +14135,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ActioX</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ActioX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/data/project-board.xlsx
+++ b/data/project-board.xlsx
@@ -13713,12 +13713,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13740,12 +13740,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13767,12 +13767,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
@@ -13811,12 +13811,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -13838,12 +13838,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -13865,12 +13865,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13892,12 +13892,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -14000,12 +14000,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -14027,12 +14027,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/data/project-board.xlsx
+++ b/data/project-board.xlsx
@@ -13658,7 +13658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" customWidth="1" min="1" max="1"/>
@@ -13666,6 +13666,7 @@
     <col width="12.83203125" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13694,6 +13695,11 @@
           <t>Rollout Date</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Updated At</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13721,6 +13727,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:14:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13748,6 +13759,11 @@
           <t>2026-10-30</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:14:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13775,6 +13791,11 @@
           <t>2026-11-30</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:14:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13792,6 +13813,11 @@
           <t>v1.0</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-22T10:20:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13819,6 +13845,11 @@
           <t>2026-07-03</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:05:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13846,6 +13877,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:05:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13873,6 +13909,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:05:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13900,6 +13941,11 @@
           <t>2026-06-25</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:28:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13927,6 +13973,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:28:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13954,6 +14005,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:28:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13981,6 +14037,11 @@
           <t>2026-07-03</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-22T16:50:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14008,6 +14069,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-22T16:50:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14035,6 +14101,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-22T16:50:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14054,12 +14125,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:37:00</t>
         </is>
       </c>
     </row>
@@ -14081,12 +14157,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:37:00</t>
         </is>
       </c>
     </row>
@@ -14116,6 +14197,11 @@
           <t>2026-09-05</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:42:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14143,6 +14229,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:42:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14168,6 +14259,11 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:42:00</t>
         </is>
       </c>
     </row>

--- a/data/project-board.xlsx
+++ b/data/project-board.xlsx
@@ -11,6 +11,7 @@
     <sheet name="HR-Assist" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ReleaseAssist" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Versions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Generic Service's" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -13658,7 +13659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" customWidth="1" min="1" max="1"/>
@@ -13837,12 +13838,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13869,12 +13870,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13901,12 +13902,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13933,12 +13934,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13965,12 +13966,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13997,12 +13998,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14029,12 +14030,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14061,12 +14062,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -14093,12 +14094,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -14264,6 +14265,427 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-09-22T11:42:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Generic Service's</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Generic Service's</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Generic Service's</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Generic Service's</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:00:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Feature Group</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Group Description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Feature Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DATA &amp; RETRIEVAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Generic Retrieval Service</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Multi-Source Hybrid Retrieval</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Shared retrieval layer usable across projects and models</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Combines vector similarity and keyword search across configured data sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DATA &amp; RETRIEVAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Generic Retrieval Service</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Configurable Chunking &amp; Embedding Pipeline</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Shared retrieval layer usable across projects and models</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tunable chunk size, overlap and embedding model per source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DATA &amp; RETRIEVAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Generic Retrieval Service</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Relevance Re-Ranking</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Shared retrieval layer usable across projects and models</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Re-scores retrieved results before they reach the caller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SPEECH &amp; AUDIO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Generic Speech Service</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Real-Time Speech-to-Text</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Shared speech-to-text and text-to-speech layer for any project</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Streams live audio to text with low latency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SPEECH &amp; AUDIO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Generic Speech Service</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Multi-Language Text-to-Speech</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Shared speech-to-text and text-to-speech layer for any project</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Synthesizes natural speech across supported languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SPEECH &amp; AUDIO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Generic Speech Service</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Speaker Diarization &amp; VAD</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Shared speech-to-text and text-to-speech layer for any project</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Separates speakers and detects voice activity in a stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MODEL INFERENCE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Generic Inference Service</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Model-Agnostic Inference Routing</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Shared inference routing layer across model providers</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Routes requests across OpenAI, Anthropic and local models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MODEL INFERENCE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Generic Inference Service</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Automatic Batching &amp; Queuing</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Shared inference routing layer across model providers</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Batches concurrent requests and manages backpressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MODEL INFERENCE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Generic Inference Service</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Usage Metering &amp; Cost Tracking</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Shared inference routing layer across model providers</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tracks tokens, calls and cost per request and per caller.</t>
         </is>
       </c>
     </row>
